--- a/游戏开箱文/开箱No.022-Moon Princess.xlsx
+++ b/游戏开箱文/开箱No.022-Moon Princess.xlsx
@@ -1479,6 +1479,9 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:F21" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -1784,6 +1787,9 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:F76" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/游戏开箱文/开箱No.022-Moon Princess.xlsx
+++ b/游戏开箱文/开箱No.022-Moon Princess.xlsx
@@ -10,7 +10,7 @@
     <sheet name="说明" sheetId="1" r:id="rId1"/>
     <sheet name="開箱 No.022 Moon Princess" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -838,7 +838,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -861,6 +861,18 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1472,7 +1484,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
     </row>
@@ -1500,287 +1512,287 @@
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:1">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="8" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="4" ht="19" customHeight="1" spans="1:1">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="9" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" ht="15" spans="1:1">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="10" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" ht="15" spans="1:1">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="10" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" ht="15" spans="1:1">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="10" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" ht="15" spans="1:1">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="10" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="9" ht="15" spans="1:1">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" ht="15" spans="1:1">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="10" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="11" ht="15" spans="1:1">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:1">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:1">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="9" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="14" ht="30" spans="1:1">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="10" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="15" ht="15" spans="1:1">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="10" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16" ht="15" spans="1:1">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="10" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="17" ht="15" spans="1:1">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="10" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="18" ht="15" spans="1:1">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="10" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="19" ht="15" spans="1:1">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="10" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="20" ht="15" spans="1:1">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="10" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="21" ht="15" spans="1:1">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="10" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="22" ht="15" spans="1:1">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="10" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="23" ht="15" spans="1:1">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="10" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="24" ht="254" customHeight="1" spans="1:1">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" spans="1:1">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="10" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="27" ht="19" customHeight="1" spans="1:1">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="9" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="28" ht="30" spans="1:1">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="29" ht="30" spans="1:1">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="10" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="30" ht="15" spans="1:1">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="10" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="31" ht="15" spans="1:1">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="32" ht="260" customHeight="1" spans="1:1">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" spans="1:1">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="10" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="35" ht="19" customHeight="1" spans="1:1">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="9" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="36" ht="19" customHeight="1" spans="1:1">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="9" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="37" ht="30" spans="1:1">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="10" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="38" ht="45" spans="1:1">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="10" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="39" ht="30" spans="1:1">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="10" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="40" ht="30" spans="1:1">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="10" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="41" ht="19" customHeight="1" spans="1:1">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="9" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="42" ht="30" spans="1:1">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="10" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="43" ht="30" spans="1:1">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="10" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="44" ht="19" customHeight="1" spans="1:1">
-      <c r="A44" s="5" t="s">
+      <c r="A44" s="9" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="45" ht="90" spans="1:1">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="10" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="46" ht="45" spans="1:1">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="10" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="47" ht="30" spans="1:1">
-      <c r="A47" s="6" t="s">
+      <c r="A47" s="10" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="48" ht="19" customHeight="1" spans="1:1">
-      <c r="A48" s="5" t="s">
+      <c r="A48" s="9" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="49" ht="19" customHeight="1" spans="1:1">
-      <c r="A49" s="5" t="s">
+      <c r="A49" s="9" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="50" ht="15" spans="1:1">
-      <c r="A50" s="6" t="s">
+      <c r="A50" s="10" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="51" ht="15" spans="1:1">
-      <c r="A51" s="6" t="s">
+      <c r="A51" s="10" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="52" ht="15" spans="1:1">
-      <c r="A52" s="6" t="s">
+      <c r="A52" s="10" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="53" ht="19" customHeight="1" spans="1:1">
-      <c r="A53" s="5" t="s">
+      <c r="A53" s="9" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="54" ht="15" spans="1:1">
-      <c r="A54" s="6" t="s">
+      <c r="A54" s="10" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="55" ht="15" spans="1:1">
-      <c r="A55" s="6" t="s">
+      <c r="A55" s="10" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="56" ht="30" spans="1:1">
-      <c r="A56" s="6" t="s">
+      <c r="A56" s="10" t="s">
         <v>51</v>
       </c>
     </row>
